--- a/S_数据表/Npc_Template.xlsx
+++ b/S_数据表/Npc_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FCE580-D006-4A49-9C46-8440F4B142A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4929A4-4757-48D8-9AF3-1FFE6C5BCB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2711,15 +2711,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>11001;11003;11004;11005;11006;11007;11008;11009;11011;11012;11013;11014;11015;11016;11019;11020;12001;12002;12004;12006;12007;12008;12010;12011;12012;12013;12016;13001;13002;13003;13005;13007;13009;13010;13012;13013;13014;13016;14001;14002;14004;14006;14007;14008;14010;14011;14012;14015;15001;15002;15003;15005;15006;15007;15009;15011;15012;15013;15015;15101;15102;15103;15104;15105;15106;15107;15108;15109;15110;15111;15201;15202;15203;15204;15205;15206;15207;15208;15209;15210;15211;40001;40002;40003;40004;40005;40006;40007;40008;40009;40010;40011;40012;40101;40102;40103;40104;40105;40106;40107;40108;40109;40110;40111;40112;50101;50102;50103;50104;50201;50202;50203;50204;50301;50302;50303;50304;50401;50402;50403;50404;50501;50502;50503;50504;50601;50602;50603;50604;40201;40202;40203;40204;40205;40206;40207;40208;40209;40210;40211;40212;40301;40302;40303;40304;40305;40306;40307;40308;40309;40310;40311;40312;40401;40402;40403;40404;40405;40406;40407;40408;40409;40410;40411;40412</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>21001;21002;21003;21004;21005;21006;21007;21011;21012;21013;21014;21015;21016;21017;22001;22002;22003;22004;22005;22006;22007;22011;22012;22013;22014;22015;22016;22017;22018;22019;23001;23002;23003;23004;23005;23006;23007;23011;23012;23013;23014;23015;23016;23017;23018;23019;24001;24002;24003;24004;24005;24006;24007;24011;24012;24013;24014;24015;24016;24017;25001;25002;25003;25004;25005;25006;25007;25011;25012;25013;25014;25015;25016;25017</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>神秘商人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11001;11003;11004;11005;11006;11007;11008;11009;11011;11012;11013;11014;11015;11016;11019;11020;12001;12002;12004;12006;12007;12008;12010;12011;12012;12013;12016;13001;13002;13003;13005;13007;13009;13010;13012;13013;13014;13016;14001;14002;14004;14006;14007;14008;14010;14011;14012;14015;15001;15002;15003;15005;15006;15007;15009;15011;15012;15013;15015;15101;15102;15103;15104;15105;15106;15107;15108;15109;15110;15111;15201;15202;15203;15204;15205;15206;15207;15208;15209;15210;15211;15301;15302;15303;15304;15305;15306;15307;15308;15309;15310;15311;40001;40002;40003;40004;40005;40006;40007;40008;40009;40010;40011;40012;40101;40102;40103;40104;40105;40106;40107;40108;40109;40110;40111;40112;50101;50102;50103;50104;50201;50202;50203;50204;50301;50302;50303;50304;50401;50402;50403;50404;50501;50502;50503;50504;50601;50602;50603;50604;40201;40202;40203;40204;40205;40206;40207;40208;40209;40210;40211;40212;40301;40302;40303;40304;40305;40306;40307;40308;40309;40310;40311;40312;40401;40402;40403;40404;40405;40406;40407;40408;40409;40410;40411;40412</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O39" s="13"/>
       <c r="P39" s="30" t="s">
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="O40" s="13"/>
       <c r="P40" s="30" t="s">
@@ -8158,7 +8158,7 @@
         <v>124</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>381</v>
@@ -8215,7 +8215,7 @@
         <v>125</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>381</v>
@@ -8272,7 +8272,7 @@
         <v>126</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>381</v>
@@ -8329,7 +8329,7 @@
         <v>127</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>381</v>
@@ -8386,7 +8386,7 @@
         <v>128</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>381</v>
